--- a/data/trans_orig/IP07_C15_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C15_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio en 2023 (tasa de respuesta: 92,89%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio/instituto en 2023 (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,57 +725,57 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5681</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12516</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5331</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11977</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41367</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34532</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>45015</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>55705</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>49059</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>60210</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44379</t>
+          <t>32208</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37220</t>
+          <t>28155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>35294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>100085</t>
+          <t>73575</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91017</t>
+          <t>66206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106837</t>
+          <t>78089</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47048</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47048</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47048</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>61036</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>61036</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>61036</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>111354</t>
+          <t>84669</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>111354</t>
+          <t>84669</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111354</t>
+          <t>84669</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8199</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4545</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12132</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4603</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7909</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>18135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13614</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9681</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17268</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>62,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>79,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13807</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16507</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>74,99%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>22048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33283</t>
+          <t>31495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21813</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21813</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21813</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18410</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18410</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18410</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>40183</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>40183</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>40183</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>492</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,42 +1814,42 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>75,93%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3696</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>18,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3351</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -1862,74 +1862,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16939</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14313</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2486</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2556</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>24,07%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>19201</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>16163</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>19496</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2444</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>18,28%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2538</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>13689</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11701</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14145</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>14532</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12276</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15022</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>81,72%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>19982</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>60</t>
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>33671</t>
+          <t>34817</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31592</t>
+          <t>32769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34127</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>14145</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14145</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14145</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>34127</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34127</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34127</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5045</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9314</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,71%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>57,14%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6945</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>42,66%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6986</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14066</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>69,05%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>42,86%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,29%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>12544</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9336</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>14985</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>77,05%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>57,34%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>24370</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28662</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>83,83%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>16300</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>16300</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>16300</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3087</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13360</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>18,42%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>34,92%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>6586</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3079</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10663</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>28,95%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20823</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>31207</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>24895</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>35168</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>81,58%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>65,08%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>91,93%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>16164</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>12087</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>19671</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>53,13%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>86,47%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>17174</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34631</t>
+          <t>20617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>48380</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>41084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51809</t>
+          <t>53636</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>38255</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>38255</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>38255</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>22750</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>22750</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>22750</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37344</t>
+          <t>24073</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37344</t>
+          <t>24073</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37344</t>
+          <t>24073</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>60093</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>60093</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60093</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,107 +3121,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2277</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -3234,74 +3234,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>61967</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>60747</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>62351</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>68853</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>67335</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>69202</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>81315</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>178</t>
@@ -3309,27 +3309,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>143283</t>
+          <t>156101</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>141390</t>
+          <t>154375</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>143667</t>
+          <t>156450</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>62351</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>62351</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>62351</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>69202</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>69202</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>69202</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>143667</t>
+          <t>156450</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>143667</t>
+          <t>156450</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>143667</t>
+          <t>156450</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>26465</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>18627</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>37449</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>21260</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>11854</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>30319</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>48409</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36702</t>
+          <t>37331</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>221917</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>210933</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>229755</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>177535</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>168476</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>186941</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>222009</t>
+          <t>163457</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>210173</t>
+          <t>155325</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>231171</t>
+          <t>169943</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>399545</t>
+          <t>385374</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>385422</t>
+          <t>373139</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>412476</t>
+          <t>396452</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
